--- a/JsonConverter/ExcelFiles/OO_CookingCueSheet.xlsx
+++ b/JsonConverter/ExcelFiles/OO_CookingCueSheet.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,12 @@
       <b val="1"/>
     </font>
     <font/>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +56,11 @@
         <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -65,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -75,6 +84,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -441,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -549,6 +561,16 @@
           <t>기본 상태 문구</t>
         </is>
       </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>절구 튜토리얼 ID</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>절구 도구 ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -636,6 +658,16 @@
           <t>string</t>
         </is>
       </c>
+      <c r="R2" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="S2" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -723,6 +755,16 @@
           <t>DefaultStatusText</t>
         </is>
       </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>JulguTutorialId</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>JulguToolId</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -788,6 +830,16 @@
       <c r="Q4" t="inlineStr">
         <is>
           <t>재료를 집어 알맞은 조리도구 위에 올려주세요.</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>narration_tutorial_14</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>Julgu</t>
         </is>
       </c>
     </row>
